--- a/automation/mrz_kamerun_objekte/Meta_Kamerun_Objekte.xlsx
+++ b/automation/mrz_kamerun_objekte/Meta_Kamerun_Objekte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sszgua\git\opendatazurich.github.io\automation\mrz_kamerun_objekte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B29F26C6-4A00-482E-95C2-3E958D896467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8F433E-A528-4EB3-AA86-38819D184685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1433,93 +1433,6 @@
     <t>Andere (nicht offen)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;![CDATA[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="3" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="3" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Das Museum Rietberg besitzt seit Gründung des einige Objekte aus Kamerun und über die Jahre kamen noch einige weitere dazu. Jonas Lendenmann hat im Zuge eines CAS zur Provenienzforschung die Sammlung einen Überblick über die Provenienzen erstellt. Seine Arbeit gibt einen ausführlichen Einblick und auch Kontextinformationen zur Sammlung, ihrer Entstehung sowie Ausstellungstätigkeiten und Kooperationen. Die Arbeit ist auf der Webseite des Museum Rietbergs zum download verfügbar. Der vorliegende Datensatz ist die von ihm aufgearbeiteten Daten zu den Sammlungsobjekten aus Kamerun.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="3" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>]]&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;![CDATA[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Die Daten zum Zeitpunkt der Erstpublikation entsprechen den Informationen, wie sie von Jonas Lendenmann in seiner Arbeit erstellt hat. Da die Forschung und Arbeit an diesen Sammlungsobjekten jedoch nicht abgeschlossen ist, wird wöchentlich ein Abgleich gemacht. Wie oft tatsächlich Änderungen passieren, kann nicht im Voraus gesagt werden. Die Daten werden als ein JSON-File publiziert, mit den Sammlungsobjekten als Objekte.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>]]&gt;</t>
-    </r>
-  </si>
-  <si>
     <t>Provenienz_Output</t>
   </si>
   <si>
@@ -1536,6 +1449,12 @@
   </si>
   <si>
     <t>Stadt Zürich</t>
+  </si>
+  <si>
+    <t>Das Museum Rietberg besitzt seit Gründung des einige Objekte aus Kamerun und über die Jahre kamen noch einige weitere dazu. Jonas Lendenmann hat im Zuge eines CAS zur Provenienzforschung die Sammlung einen Überblick über die Provenienzen erstellt. Seine Arbeit gibt einen ausführlichen Einblick und auch Kontextinformationen zur Sammlung, ihrer Entstehung sowie Ausstellungstätigkeiten und Kooperationen. Die Arbeit ist auf der Webseite des Museum Rietbergs zum download verfügbar. Der vorliegende Datensatz ist die von ihm aufgearbeiteten Daten zu den Sammlungsobjekten aus Kamerun.</t>
+  </si>
+  <si>
+    <t>Die Daten zum Zeitpunkt der Erstpublikation entsprechen den Informationen, wie sie von Jonas Lendenmann in seiner Arbeit erstellt hat. Da die Forschung und Arbeit an diesen Sammlungsobjekten jedoch nicht abgeschlossen ist, wird wöchentlich ein Abgleich gemacht. Wie oft tatsächlich Änderungen passieren, kann nicht im Voraus gesagt werden. Die Daten werden als ein JSON-File publiziert, mit den Sammlungsobjekten als Objekte.</t>
   </si>
 </sst>
 </file>
@@ -1904,7 +1823,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
@@ -2004,6 +1923,9 @@
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -2310,7 +2232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="4" customFormat="1" ht="153" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" s="4" customFormat="1" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>12</v>
       </c>
@@ -2320,8 +2242,8 @@
       <c r="C3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>317</v>
+      <c r="D3" s="34" t="s">
+        <v>323</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="8" t="s">
@@ -2373,7 +2295,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="8" t="s">
@@ -2461,7 +2383,7 @@
         <v>21</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="7" t="s">
@@ -2604,15 +2526,15 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:6" ht="89.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>67</v>
       </c>
       <c r="B21" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="21" t="s">
-        <v>318</v>
+      <c r="C21" s="35" t="s">
+        <v>324</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="7"/>
@@ -3194,7 +3116,7 @@
         <v>78</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C62" s="21" t="s">
         <v>170</v>
@@ -3254,13 +3176,13 @@
         <v>78</v>
       </c>
       <c r="B66" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="D66" s="21" t="s">
         <v>319</v>
-      </c>
-      <c r="C66" s="21" t="s">
-        <v>320</v>
-      </c>
-      <c r="D66" s="21" t="s">
-        <v>321</v>
       </c>
       <c r="E66" s="7"/>
     </row>
@@ -4194,26 +4116,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="637d3f4c-beee-42dd-a17b-93f7589025e5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="31d8624d-d3e1-4449-addd-518bfa42d279">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010036EB69643BC4D84A90CF31D6917ED8B0" ma:contentTypeVersion="17" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e787fa9c9cb978e1d00e8cc5d4e605d2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31d8624d-d3e1-4449-addd-518bfa42d279" xmlns:ns3="637d3f4c-beee-42dd-a17b-93f7589025e5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="369004915ca410f163a62304f925ff92" ns2:_="" ns3:_="">
     <xsd:import namespace="31d8624d-d3e1-4449-addd-518bfa42d279"/>
@@ -4462,32 +4364,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6056489-A7A4-4445-AFC5-87E5586E5E93}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="31d8624d-d3e1-4449-addd-518bfa42d279"/>
-    <ds:schemaRef ds:uri="637d3f4c-beee-42dd-a17b-93f7589025e5"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B3AD83-9986-4E71-995F-A94C1CED6EB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="637d3f4c-beee-42dd-a17b-93f7589025e5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="31d8624d-d3e1-4449-addd-518bfa42d279">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B249E2D-022F-440D-B037-6C32F5252DA3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4504,4 +4401,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B3AD83-9986-4E71-995F-A94C1CED6EB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6056489-A7A4-4445-AFC5-87E5586E5E93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="31d8624d-d3e1-4449-addd-518bfa42d279"/>
+    <ds:schemaRef ds:uri="637d3f4c-beee-42dd-a17b-93f7589025e5"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/automation/mrz_kamerun_objekte/Meta_Kamerun_Objekte.xlsx
+++ b/automation/mrz_kamerun_objekte/Meta_Kamerun_Objekte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sszgua\git\opendatazurich.github.io\automation\mrz_kamerun_objekte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8F433E-A528-4EB3-AA86-38819D184685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F54487-69B8-48E1-A39B-24570076620F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="kategorien" localSheetId="1">kategorien_werteliste!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191028" concurrentCalc="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="316">
   <si>
     <t>Tagname</t>
   </si>
@@ -729,9 +729,6 @@
     <t>URL_SammlungenOnline</t>
   </si>
   <si>
-    <t>URL auf die Sammlungen Online des Museum Rietberg</t>
-  </si>
-  <si>
     <t>Objekttyp</t>
   </si>
   <si>
@@ -773,9 +770,6 @@
     <t>Geographischer Bezug</t>
   </si>
   <si>
-    <t>Sämtliche geographische Bezüge. Es gibt bis zu drei verschiedene Angaben: Heutige administrative Einteilung (z.B. "Kamerun"), Geographisch-natürliche Regionen ("z.B. "Alpen") und Historische Regionen, welche keiner heutigen, genau definierten administrativer Einteilung entspricht (z.B. "Kameruner Grasland")</t>
-  </si>
-  <si>
     <t>Urheber*innen</t>
   </si>
   <si>
@@ -812,9 +806,6 @@
     <t>Wikidata-ID der Urheber*in</t>
   </si>
   <si>
-    <t>Wikidata Identifier der Urheber*in, falls vorhanden</t>
-  </si>
-  <si>
     <t>Titel_Bezeichnungen</t>
   </si>
   <si>
@@ -848,27 +839,18 @@
     <t>ausgeschriebene Datierung</t>
   </si>
   <si>
-    <t>Ausformulierte Datierung als Text</t>
-  </si>
-  <si>
     <t>Date_Typ</t>
   </si>
   <si>
     <t>Typ der Datierung</t>
   </si>
   <si>
-    <t>Typ des Event, auf den sich die Datierung bezieht</t>
-  </si>
-  <si>
     <t>Date_Exakt</t>
   </si>
   <si>
     <t>Exakte Datierung</t>
   </si>
   <si>
-    <t>Falls sich ein Werk genau datieren lässt, ist dies hier eingetragen</t>
-  </si>
-  <si>
     <t>Date_Von</t>
   </si>
   <si>
@@ -962,18 +944,12 @@
     <t>Sortierung von Provenienzen</t>
   </si>
   <si>
-    <t>Sortierung der PV-Datensätze, um die richtige Provenienzkette zu erhalten</t>
-  </si>
-  <si>
     <t>Provenienz_ID</t>
   </si>
   <si>
     <t>ID der Provenienz</t>
   </si>
   <si>
-    <t xml:space="preserve">ID des Datensatz des PV. PV können mehrere Objekte beinhalten (z.B. Schenkung einer Sammlung), allerdings werden sie hier pro Objekt aufgelistet. Mithilfe der ID lassen sich die PV identifizieren. </t>
-  </si>
-  <si>
     <t>Provenienz_HistNr</t>
   </si>
   <si>
@@ -989,9 +965,6 @@
     <t>Wikidata-ID der Person des PV</t>
   </si>
   <si>
-    <t>QID von wikidata der Person des PV</t>
-  </si>
-  <si>
     <t>Name der Person</t>
   </si>
   <si>
@@ -1124,27 +1097,18 @@
     <t>Eintrag im Feld "administrativ"</t>
   </si>
   <si>
-    <t>Mit Administrativ sind heutige politische Orte oder Regionen gemeint</t>
-  </si>
-  <si>
     <t>Geo_ungesichert</t>
   </si>
   <si>
     <t>Unsicherheit über die Angabe</t>
   </si>
   <si>
-    <t>Boolean. Wenn "True", dann ist die Angabe im Feld Geo_Administrativ nicht gesichert</t>
-  </si>
-  <si>
     <t>Geo_QID</t>
   </si>
   <si>
     <t>WIkidata-ID des Ortes</t>
   </si>
   <si>
-    <t>Falls vorhanden, wird die QID des Ortes angegeben</t>
-  </si>
-  <si>
     <t>Geo_geonames</t>
   </si>
   <si>
@@ -1154,36 +1118,6 @@
     <t>Falls vorhanden, wird die Geonames-ID des Ortes angegeben</t>
   </si>
   <si>
-    <t>Untenstehende Angaben sind nur für das ODZ-Team relevant:</t>
-  </si>
-  <si>
-    <t>ressourcen</t>
-  </si>
-  <si>
-    <t>Downloadressourcen</t>
-  </si>
-  <si>
-    <t>dateiname</t>
-  </si>
-  <si>
-    <t>Falls in einem Dataset Links UND Downloadfiles vorkommen, braucht es für letzteres hier die Nennung der Ressource.</t>
-  </si>
-  <si>
-    <t>ressource</t>
-  </si>
-  <si>
-    <t>messwerte_mythenquai_2007-2017.csv</t>
-  </si>
-  <si>
-    <t>Zeitreihe der 10-minütig gemessenen Werte seit 2017 an der Messstation Mythenquai.</t>
-  </si>
-  <si>
-    <t>messwerte_tiefenbrunnen_2007-2017.csv</t>
-  </si>
-  <si>
-    <t>Zeitreihe der 10-minütig gemessenen Werte seit 2017 an der Messstation Tiefenbrunnen.</t>
-  </si>
-  <si>
     <t>Werte</t>
   </si>
   <si>
@@ -1439,9 +1373,6 @@
     <t>Ausgabe der Provenienz als String</t>
   </si>
   <si>
-    <t>Die Metadaten der Provenienz als Ausgabe zusammengefasst. Teilweise werden noch händische Änderungen oder Anpassungen gemacht.</t>
-  </si>
-  <si>
     <t>Provenienz_Person_Label</t>
   </si>
   <si>
@@ -1451,10 +1382,55 @@
     <t>Stadt Zürich</t>
   </si>
   <si>
-    <t>Das Museum Rietberg besitzt seit Gründung des einige Objekte aus Kamerun und über die Jahre kamen noch einige weitere dazu. Jonas Lendenmann hat im Zuge eines CAS zur Provenienzforschung die Sammlung einen Überblick über die Provenienzen erstellt. Seine Arbeit gibt einen ausführlichen Einblick und auch Kontextinformationen zur Sammlung, ihrer Entstehung sowie Ausstellungstätigkeiten und Kooperationen. Die Arbeit ist auf der Webseite des Museum Rietbergs zum download verfügbar. Der vorliegende Datensatz ist die von ihm aufgearbeiteten Daten zu den Sammlungsobjekten aus Kamerun.</t>
-  </si>
-  <si>
-    <t>Die Daten zum Zeitpunkt der Erstpublikation entsprechen den Informationen, wie sie von Jonas Lendenmann in seiner Arbeit erstellt hat. Da die Forschung und Arbeit an diesen Sammlungsobjekten jedoch nicht abgeschlossen ist, wird wöchentlich ein Abgleich gemacht. Wie oft tatsächlich Änderungen passieren, kann nicht im Voraus gesagt werden. Die Daten werden als ein JSON-File publiziert, mit den Sammlungsobjekten als Objekte.</t>
+    <t>Sämtliche geographische Bezüge. Es gibt bis zu drei verschiedene Angaben: Heutige administrative Einteilung (z.B. "Kamerun"), geographisch-natürliche Regionen ("z.B. "Alpen") und historische (politisch oder kulturell definierte) Regionen, welche keiner heutigen, genau definierten administrativer Einteilung entsprechen (z.B. "Kameruner Grasland")</t>
+  </si>
+  <si>
+    <t>URL auf die Sammlungen Online des Museums Rietberg</t>
+  </si>
+  <si>
+    <t>Name der*des Urheber*in</t>
+  </si>
+  <si>
+    <t>Wikidata Identifier der*des Urheber*in, falls vorhanden</t>
+  </si>
+  <si>
+    <t>Ausformulierte Datierung</t>
+  </si>
+  <si>
+    <t>Typ des Events, auf den sich die Datierung bezieht</t>
+  </si>
+  <si>
+    <t>Falls sich ein Werk genau datieren lässt, ist diese Datierung hier eingetragen</t>
+  </si>
+  <si>
+    <t>Sortierung der PV-Datensätze, um die richtige Provenienzkette zu erhalten (1 = Urheber)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID des Datensatz des PVs. PVs können mehrere Objekte beinhalten (z.B. Schenkung einer Sammlung), allerdings werden sie hier pro Objekt aufgelistet. Mithilfe der ID lassen sich die PV identifizieren. </t>
+  </si>
+  <si>
+    <t>Identifier (Q-ID) von Wikidata der Person des PV</t>
+  </si>
+  <si>
+    <t>Die Metadaten der Provenienz als Textausgabe zusammengefasst. Teilweise werden hier noch händische Änderungen oder Anpassungen gemacht.</t>
+  </si>
+  <si>
+    <t>Mit "administrativ" sind heutige politische Orte oder Regionen gemeint, siehe oben</t>
+  </si>
+  <si>
+    <t>Boolean. Wenn "True", dann ist die Angabe unter "Geo_Administrativ" nicht gesichert</t>
+  </si>
+  <si>
+    <t>Falls vorhanden, wird der Wikidata Identifier (QID) des Ortes angegeben</t>
+  </si>
+  <si>
+    <t>Die Daten zum Zeitpunkt der Erstpublikation entsprechen den Informationen, wie sie von Jonas Lendenmann in seiner Arbeit erhoben und dokumentiert wurden. Da die Forschung und Arbeit an diesen Sammlungsobjekten jedoch noch nicht abgeschlossen ist, erfolgt wöchentlich ein Abgleich der Daten. Wie häufig tatsächlich Änderungen auftreten, lässt sich im Voraus nicht bestimmen.
+Die Daten werden als JSON-Datei veröffentlicht, in der die Sammlungsobjekte als einzelne Objekte strukturiert sind.</t>
+  </si>
+  <si>
+    <t>Das Museum Rietberg verfügt seit seiner Gründung über erste Objekte aus Kamerun; im Laufe der Jahre wurde dieser Bestand kontinuierlich erweitert. Im Rahmen eines CAS in Provenienzforschung hat Jonas Lendenmann einen umfassenden Überblick über die Provenienzen dieser Sammlung erarbeitet. Seine Studie bietet nicht nur detaillierte Einblicke in die Herkunft der Objekte, sondern liefert auch wichtige Kontextinformationen zur Sammlungsgeschichte, zu Ausstellungstätigkeiten sowie zu Kooperationen des Museums.
+Die vollständige Arbeit steht auf der Webseite des Museum Rietberg zum Download bereit.
+Der vorliegende Datensatz basiert auf den von Jonas Lendenmann recherchierten und aufbereiteten Informationen zu den Sammlungsobjekten aus Kamerun.</t>
   </si>
 </sst>
 </file>
@@ -2178,7 +2154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="255.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="11" customWidth="1"/>
@@ -2232,7 +2208,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="4" customFormat="1" ht="127.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" s="4" customFormat="1" ht="178.5" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>12</v>
       </c>
@@ -2243,7 +2219,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="8" t="s">
@@ -2295,7 +2271,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="8" t="s">
@@ -2383,7 +2359,7 @@
         <v>21</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="7" t="s">
@@ -2526,7 +2502,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:6" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>67</v>
       </c>
@@ -2534,7 +2510,7 @@
         <v>70</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="7"/>
@@ -2669,7 +2645,7 @@
         <v>88</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>89</v>
+        <v>301</v>
       </c>
       <c r="E32" s="7"/>
     </row>
@@ -2678,17 +2654,17 @@
         <v>78</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -2696,28 +2672,28 @@
         <v>78</v>
       </c>
       <c r="B34" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="C34" s="21" t="s">
+      <c r="D34" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" s="4" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A35" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="E34" s="7"/>
-    </row>
-    <row r="35" spans="1:6" s="4" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" s="21" t="s">
+      <c r="C35" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="21" t="s">
-        <v>96</v>
-      </c>
       <c r="D35" s="21" t="s">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="E35" s="7"/>
     </row>
@@ -2726,13 +2702,13 @@
         <v>78</v>
       </c>
       <c r="B36" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="21" t="s">
         <v>98</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>100</v>
       </c>
       <c r="E36" s="7"/>
     </row>
@@ -2741,13 +2717,13 @@
         <v>78</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E37" s="7"/>
     </row>
@@ -2756,13 +2732,13 @@
         <v>78</v>
       </c>
       <c r="B38" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D38" s="21" t="s">
         <v>103</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>105</v>
       </c>
       <c r="E38" s="7"/>
     </row>
@@ -2771,13 +2747,13 @@
         <v>78</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>107</v>
+        <v>302</v>
       </c>
       <c r="E39" s="7"/>
     </row>
@@ -2786,13 +2762,13 @@
         <v>78</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>110</v>
+        <v>303</v>
       </c>
       <c r="E40" s="7"/>
     </row>
@@ -2801,13 +2777,13 @@
         <v>78</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E41" s="7"/>
     </row>
@@ -2822,7 +2798,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E42" s="7"/>
     </row>
@@ -2831,13 +2807,13 @@
         <v>78</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E43" s="7"/>
     </row>
@@ -2846,13 +2822,13 @@
         <v>78</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E44" s="7"/>
     </row>
@@ -2861,13 +2837,13 @@
         <v>78</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>122</v>
+        <v>304</v>
       </c>
       <c r="E45" s="7"/>
     </row>
@@ -2876,28 +2852,28 @@
         <v>78</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>125</v>
+        <v>305</v>
       </c>
       <c r="E46" s="7"/>
     </row>
-    <row r="47" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A47" s="11" t="s">
         <v>78</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>128</v>
+        <v>306</v>
       </c>
       <c r="E47" s="7"/>
     </row>
@@ -2906,13 +2882,13 @@
         <v>78</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E48" s="7"/>
     </row>
@@ -2921,13 +2897,13 @@
         <v>78</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E49" s="7"/>
     </row>
@@ -2936,13 +2912,13 @@
         <v>78</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E50" s="7"/>
     </row>
@@ -2951,13 +2927,13 @@
         <v>78</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E51" s="7"/>
     </row>
@@ -2966,13 +2942,13 @@
         <v>78</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E52" s="7"/>
     </row>
@@ -2981,13 +2957,13 @@
         <v>78</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E53" s="7"/>
     </row>
@@ -2996,13 +2972,13 @@
         <v>78</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E54" s="7"/>
     </row>
@@ -3011,13 +2987,13 @@
         <v>78</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E55" s="7"/>
     </row>
@@ -3026,13 +3002,13 @@
         <v>78</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E56" s="7"/>
     </row>
@@ -3041,13 +3017,13 @@
         <v>78</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E57" s="7"/>
     </row>
@@ -3056,13 +3032,13 @@
         <v>78</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>160</v>
+        <v>307</v>
       </c>
       <c r="E58" s="7"/>
     </row>
@@ -3071,13 +3047,13 @@
         <v>78</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>163</v>
+        <v>308</v>
       </c>
       <c r="E59" s="7"/>
     </row>
@@ -3086,13 +3062,13 @@
         <v>78</v>
       </c>
       <c r="B60" s="21" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E60" s="7"/>
     </row>
@@ -3101,13 +3077,13 @@
         <v>78</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>169</v>
+        <v>309</v>
       </c>
       <c r="E61" s="7"/>
     </row>
@@ -3116,13 +3092,13 @@
         <v>78</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="E62" s="7"/>
     </row>
@@ -3131,13 +3107,13 @@
         <v>78</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E63" s="7"/>
     </row>
@@ -3146,13 +3122,13 @@
         <v>78</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="E64" s="7"/>
     </row>
@@ -3161,13 +3137,13 @@
         <v>78</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="E65" s="7"/>
     </row>
@@ -3176,13 +3152,13 @@
         <v>78</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="E66" s="7"/>
     </row>
@@ -3191,13 +3167,13 @@
         <v>78</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="E67" s="7"/>
     </row>
@@ -3206,13 +3182,13 @@
         <v>78</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E68" s="7"/>
     </row>
@@ -3221,13 +3197,13 @@
         <v>78</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E69" s="7"/>
     </row>
@@ -3236,13 +3212,13 @@
         <v>78</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E70" s="7"/>
     </row>
@@ -3251,13 +3227,13 @@
         <v>78</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="E71" s="7"/>
     </row>
@@ -3266,13 +3242,13 @@
         <v>78</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="E72" s="7"/>
     </row>
@@ -3281,13 +3257,13 @@
         <v>78</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E73" s="7"/>
     </row>
@@ -3296,13 +3272,13 @@
         <v>78</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E74" s="7"/>
     </row>
@@ -3311,13 +3287,13 @@
         <v>78</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E75" s="7"/>
     </row>
@@ -3326,13 +3302,13 @@
         <v>78</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="E76" s="7"/>
     </row>
@@ -3341,13 +3317,13 @@
         <v>78</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E77" s="7"/>
     </row>
@@ -3356,13 +3332,13 @@
         <v>78</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="E78" s="7"/>
     </row>
@@ -3371,174 +3347,96 @@
         <v>78</v>
       </c>
       <c r="B79" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="E79" s="7"/>
+    </row>
+    <row r="80" spans="1:5" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A80" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="E80" s="7"/>
+    </row>
+    <row r="81" spans="1:5" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A81" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B81" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="E81" s="7"/>
+    </row>
+    <row r="82" spans="1:5" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A82" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B82" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="D82" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="E82" s="7"/>
+    </row>
+    <row r="83" spans="1:5" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A83" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B83" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="C83" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="C79" s="21" t="s">
+      <c r="D83" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="D79" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="E79" s="7"/>
-    </row>
-    <row r="80" spans="1:5" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B80" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="C80" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="D80" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="E80" s="7"/>
-    </row>
-    <row r="81" spans="1:6" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A81" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B81" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="C81" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="D81" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="E81" s="7"/>
-    </row>
-    <row r="82" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A82" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B82" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="C82" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="D82" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="E82" s="7"/>
-    </row>
-    <row r="83" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A83" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B83" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="C83" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="D83" s="21" t="s">
-        <v>223</v>
-      </c>
       <c r="E83" s="7"/>
     </row>
-    <row r="84" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="11"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
     </row>
-    <row r="85" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="11"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
     </row>
-    <row r="86" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="11"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
-    </row>
-    <row r="87" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="11"/>
-      <c r="B87" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C87" s="3"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-    </row>
-    <row r="88" spans="1:6" s="4" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="11"/>
-      <c r="B88" s="3"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="6"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A89" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B89" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C89" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="4"/>
-    </row>
-    <row r="90" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="B90" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="C90" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D90" s="13"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A91" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B91" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="C91" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="D91" s="12"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A92" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B92" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="C92" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="D92" s="12"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B93" s="12"/>
-      <c r="C93" s="12"/>
-      <c r="D93" s="12"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.98425196850393704" bottom="0.59055118110236227" header="0.39370078740157483" footer="0.27559055118110237"/>
@@ -3570,112 +3468,112 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="29" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="29" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="29" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="29" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="29" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="29" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="29" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="29" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="29" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="29" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="29" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="29" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="29" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="29" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="29" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="31" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="32" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -3699,20 +3597,20 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" s="25" t="s">
         <v>234</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="29" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="29" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.2">
@@ -3722,25 +3620,25 @@
     </row>
     <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A6" s="30" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="31" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="32" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -3764,70 +3662,70 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" s="25" t="s">
         <v>234</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="29" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="29" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="29" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="29" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="29" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="29" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="29" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="29" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.2">
@@ -3837,17 +3735,17 @@
     </row>
     <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="29" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="29" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A17" s="30" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" x14ac:dyDescent="0.2">
@@ -3858,12 +3756,12 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="31" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="32" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15" x14ac:dyDescent="0.2">
@@ -3906,61 +3804,61 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="29" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="D2" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="29" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="B3" s="26"/>
       <c r="C3" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="D4" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="D5" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.2">
@@ -3969,140 +3867,140 @@
       </c>
       <c r="B6" s="26"/>
       <c r="C6" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="D6" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="27" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="D7" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="27" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="B8" s="26"/>
       <c r="C8" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="D8" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="29" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="B9" s="26"/>
       <c r="C9" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="D9" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="29" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="B10" s="26"/>
       <c r="C10" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="D10" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="B11" s="26"/>
       <c r="C11" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="D11" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="29" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="B12" s="26"/>
       <c r="C12" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="29" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="B13" s="26"/>
       <c r="C13" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="D13" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="29" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="B14" s="26"/>
       <c r="C14" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="D14" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="29" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B15" s="26"/>
       <c r="C15" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="D15" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="29" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="B16" s="26"/>
       <c r="C16" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="31" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="32" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="C22" s="26"/>
     </row>
@@ -4116,6 +4014,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="637d3f4c-beee-42dd-a17b-93f7589025e5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="31d8624d-d3e1-4449-addd-518bfa42d279">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010036EB69643BC4D84A90CF31D6917ED8B0" ma:contentTypeVersion="17" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e787fa9c9cb978e1d00e8cc5d4e605d2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31d8624d-d3e1-4449-addd-518bfa42d279" xmlns:ns3="637d3f4c-beee-42dd-a17b-93f7589025e5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="369004915ca410f163a62304f925ff92" ns2:_="" ns3:_="">
     <xsd:import namespace="31d8624d-d3e1-4449-addd-518bfa42d279"/>
@@ -4364,27 +4282,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B3AD83-9986-4E71-995F-A94C1CED6EB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="637d3f4c-beee-42dd-a17b-93f7589025e5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="31d8624d-d3e1-4449-addd-518bfa42d279">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6056489-A7A4-4445-AFC5-87E5586E5E93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="637d3f4c-beee-42dd-a17b-93f7589025e5"/>
+    <ds:schemaRef ds:uri="31d8624d-d3e1-4449-addd-518bfa42d279"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B249E2D-022F-440D-B037-6C32F5252DA3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4401,29 +4324,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B3AD83-9986-4E71-995F-A94C1CED6EB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6056489-A7A4-4445-AFC5-87E5586E5E93}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="31d8624d-d3e1-4449-addd-518bfa42d279"/>
-    <ds:schemaRef ds:uri="637d3f4c-beee-42dd-a17b-93f7589025e5"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>